--- a/data/Negociado_de_Policia/npprDS_tiposdelitos.xlsx
+++ b/data/Negociado_de_Policia/npprDS_tiposdelitos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Negociado_de_Policia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BE3FDE-AE04-4153-B196-79A767BA86DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9A8A57-94CF-49F1-A48F-8EC303F6AC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9408" yWindow="2100" windowWidth="11424" windowHeight="9420" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2019" sheetId="1" r:id="rId1"/>
@@ -1679,10 +1679,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1693,7 +1693,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1701,10 +1701,10 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>206</v>
+        <v>306</v>
       </c>
       <c r="C4">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1723,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1745,7 +1745,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1756,10 +1756,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C9">
-        <v>60</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1767,10 +1767,10 @@
         <v>9</v>
       </c>
       <c r="B10">
+        <v>24</v>
+      </c>
+      <c r="C10">
         <v>16</v>
-      </c>
-      <c r="C10">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1822,10 +1822,10 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
